--- a/Docs/story/Machine_Brigade_Cot_truyen_Che_do_v2.xlsx
+++ b/Docs/story/Machine_Brigade_Cot_truyen_Che_do_v2.xlsx
@@ -8004,12 +8004,12 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>amphib_light_vehicle, light_tank, armored_car, rocket_technical, mortar_carrier, zu23_technical, engineer_vehicle, scout_jeep</t>
+          <t>light_tank, armored_car, rocket_technical, mortar_carrier, zu23_technical, engineer_vehicle, scout_jeep</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>smoke_screen, artillery_barrage</t>
+          <t>artillery_barrage</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>smoke_screen, repair_drop</t>
+          <t>repair_drop</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>zu23_technical, aa_vehicle, shorad_vehicle, aa_gun_vehicle, armored_car, ifv, engineer_vehicle, mobile_repair_vehicle</t>
+          <t>zu23_technical, aa_vehicle, aa_gun_vehicle, armored_car, ifv, engineer_vehicle</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>uav_scan, repair_drop</t>
+          <t>repair_drop</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -8145,14 +8145,10 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>scout_jeep, radar_scout, counter_battery_radar, wheeled_howitzer, artillery, scout_heli, recon_drone, armored_car</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>instant_counter_battery, illum_flare_strike</t>
-        </is>
-      </c>
+          <t>scout_jeep, artillery, scout_heli, recon_drone, armored_car</t>
+        </is>
+      </c>
+      <c r="E7" s="6"/>
       <c r="F7" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -8192,14 +8188,10 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>scout_jeep, radar_scout, armored_car, recoilless_jeep, light_tank, smoke_carrier, ew_jammer, engineer_vehicle</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>smoke_screen, uav_scan</t>
-        </is>
-      </c>
+          <t>scout_jeep, armored_car, recoilless_jeep, light_tank, ew_jammer, engineer_vehicle</t>
+        </is>
+      </c>
+      <c r="E8" s="6"/>
       <c r="F8" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -8239,7 +8231,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>engineer_vehicle, demolition_line_vehicle, mine_layer, tank_destroyer, nlos_atgm_vehicle, wheeled_gun, towed_at_gun, scout_jeep</t>
+          <t>engineer_vehicle, demolition_line_vehicle, mine_layer, tank_destroyer, wheeled_gun, scout_jeep</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -8286,14 +8278,10 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>river_patrol_boat, river_gunboat, amphib_light_vehicle, coastal_ashm_vehicle, light_tank, attack_helicopter, prop_attack_plane, aa_vehicle</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>guided_shell_strike, smoke_screen</t>
-        </is>
-      </c>
+          <t>river_patrol_boat, river_gunboat, light_tank, attack_helicopter, aa_vehicle</t>
+        </is>
+      </c>
+      <c r="E10" s="6"/>
       <c r="F10" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -8333,14 +8321,10 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>microwave_vehicle, interceptor_drone_vehicle, aa_vehicle, zu23_technical, engineer_vehicle, smoke_carrier, armored_car, ifv</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>drone_intercept_strike, smoke_screen</t>
-        </is>
-      </c>
+          <t>aa_vehicle, zu23_technical, engineer_vehicle, armored_car, ifv</t>
+        </is>
+      </c>
+      <c r="E11" s="6"/>
       <c r="F11" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -8380,14 +8364,10 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>fighter_jet, light_attack_heli, attack_helicopter, wingman_drone, interceptor_drone_vehicle, microwave_vehicle, iron_beam, shorad_vehicle</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>drone_intercept_strike, jam_storm</t>
-        </is>
-      </c>
+          <t>fighter_jet, attack_helicopter, iron_beam</t>
+        </is>
+      </c>
+      <c r="E12" s="6"/>
       <c r="F12" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -8427,12 +8407,12 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>mobile_repair_vehicle, ammo_carrier, engineer_vehicle, aa_vehicle, ifv, smoke_carrier, tank_destroyer, scout_jeep</t>
+          <t>ammo_carrier, engineer_vehicle, aa_vehicle, ifv, tank_destroyer, scout_jeep</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>repair_drop, smoke_screen</t>
+          <t>repair_drop</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -8474,14 +8454,10 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>microwave_vehicle, iron_beam, interceptor_drone_vehicle, zu23_technical, aa_vehicle, engineer_vehicle, bridging_vehicle, mobile_repair_vehicle</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>drone_intercept_strike, smoke_screen</t>
-        </is>
-      </c>
+          <t>iron_beam, zu23_technical, aa_vehicle, engineer_vehicle, bridging_vehicle</t>
+        </is>
+      </c>
+      <c r="E14" s="6"/>
       <c r="F14" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -8521,14 +8497,10 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>armored_car, ifv, amphib_light_vehicle, airborne_light_tank, scout_jeep, shorad_vehicle, smoke_carrier, mobile_repair_vehicle</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>smoke_screen, decoy_paradrop</t>
-        </is>
-      </c>
+          <t>armored_car, ifv, scout_jeep</t>
+        </is>
+      </c>
+      <c r="E15" s="6"/>
       <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Đoàn xe chở Venn (vật thể kịch bản ở nền, không phải mục tiêu)</t>
@@ -8568,7 +8540,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>main_battle_tank, heavy_tank, bmpt, ifv, aa_vehicle, mlrs, tank_destroyer, artillery</t>
+          <t>main_battle_tank, heavy_tank, ifv, aa_vehicle, mlrs, tank_destroyer, artillery</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -8615,14 +8587,10 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>aa_57mm_vehicle, heavy_aa, iron_beam, sam_launcher, zu23_technical, shorad_vehicle, radar_support_vehicle, ifv</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>illum_flare_strike, sead_strike</t>
-        </is>
-      </c>
+          <t>heavy_aa, iron_beam, sam_launcher, zu23_technical, ifv</t>
+        </is>
+      </c>
+      <c r="E17" s="6"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -8662,12 +8630,12 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>combat_wreck_car, armored_bulldozer, rocket_technical, zu23_technical, recoilless_jeep, mortar_carrier, demolition_line_vehicle, vbied</t>
+          <t>armored_bulldozer, rocket_technical, zu23_technical, recoilless_jeep, mortar_carrier, demolition_line_vehicle, vbied</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>reinforcements, smoke_screen</t>
+          <t>reinforcements</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -8709,12 +8677,12 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>coastal_ashm_vehicle, ground_cruise_missile_vehicle, attack_helicopter, stealth_naval_strike, recon_drone, river_gunboat, sam_launcher, iron_beam</t>
+          <t>ground_cruise_missile_vehicle, attack_helicopter, stealth_naval_strike, recon_drone, river_gunboat, sam_launcher, iron_beam</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>cruise_missile, chaff_strike</t>
+          <t>cruise_missile</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -8756,14 +8724,10 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>amphib_light_vehicle, light_tank, river_gunboat, river_patrol_boat, coastal_ashm_vehicle, attack_helicopter, sam_launcher, airborne_vehicle</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>guided_shell_strike, smoke_screen</t>
-        </is>
-      </c>
+          <t>light_tank, river_gunboat, river_patrol_boat, attack_helicopter, sam_launcher</t>
+        </is>
+      </c>
+      <c r="E20" s="6"/>
       <c r="F20" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -8803,14 +8767,10 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>long_sam, sam_launcher, shorad_vehicle, radar_support_vehicle, aa_57mm_vehicle, iron_beam, interceptor_drone_vehicle, mobile_repair_vehicle</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>decoy_paradrop, chaff_strike</t>
-        </is>
-      </c>
+          <t>long_sam, sam_launcher, iron_beam</t>
+        </is>
+      </c>
+      <c r="E21" s="6"/>
       <c r="F21" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -8850,7 +8810,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>heavy_tank, next_gen_tank, main_battle_tank, bmpt, twin_tank, heavy_aa, mobile_repair_vehicle, ammo_carrier</t>
+          <t>heavy_tank, next_gen_tank, main_battle_tank, twin_tank, heavy_aa, ammo_carrier</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -8897,7 +8857,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>sam_launcher, aa_57mm_vehicle, iron_beam, heavy_aa, radar_support_vehicle, main_battle_tank, ifv, engineer_vehicle</t>
+          <t>sam_launcher, iron_beam, heavy_aa, main_battle_tank, ifv, engineer_vehicle</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -8944,14 +8904,10 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>fighter_jet, wingman_drone, sam_launcher, radar_support_vehicle, aa_57mm_vehicle, iron_beam, aerial_tanker, shorad_vehicle</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>chaff_strike, sead_strike</t>
-        </is>
-      </c>
+          <t>fighter_jet, sam_launcher, iron_beam</t>
+        </is>
+      </c>
+      <c r="E24" s="6"/>
       <c r="F24" s="6" t="inlineStr">
         <is>
           <t>Máy bay của Hawk (tiêm kích có tên, AI đồng minh)</t>
@@ -8991,14 +8947,10 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>recon_jet, scout_heli, armored_car, scout_jeep, smoke_carrier, ew_jammer, gps_jammer_vehicle, airborne_vehicle</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>smoke_screen, decoy_paradrop</t>
-        </is>
-      </c>
+          <t>scout_heli, armored_car, scout_jeep, ew_jammer, gps_jammer_vehicle</t>
+        </is>
+      </c>
+      <c r="E25" s="6"/>
       <c r="F25" s="6" t="inlineStr">
         <is>
           <t>—</t>
@@ -9038,7 +8990,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>main_battle_tank, bmpt, tank_destroyer, mobile_repair_vehicle, ammo_carrier, mlrs, sam_launcher, engineer_vehicle</t>
+          <t>main_battle_tank, tank_destroyer, ammo_carrier, mlrs, sam_launcher, engineer_vehicle</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
